--- a/branches/main/observations-summary.xlsx
+++ b/branches/main/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="238">
   <si>
     <t>Profile</t>
   </si>
@@ -359,7 +359,7 @@
     <t>MII PR ICU MUV Koerperlaenge</t>
   </si>
   <si>
-    <t>null#1149101003, null#8306-3</t>
+    <t>null#8306-3, null#1149101003</t>
   </si>
   <si>
     <t>mii-pr-icu-muv-kopfumfang</t>
@@ -435,21 +435,6 @@
   </si>
   <si>
     <t>integerĵ</t>
-  </si>
-  <si>
-    <t>mii-pr-icu-score-rass</t>
-  </si>
-  <si>
-    <t>MII PR ICU Score RASS</t>
-  </si>
-  <si>
-    <t>Observation Category Codes#exam</t>
-  </si>
-  <si>
-    <t>null#1345050000</t>
-  </si>
-  <si>
-    <t>dateTimeĵ</t>
   </si>
   <si>
     <t>mii-pr-icu-score-visuelle-analogskala</t>
@@ -874,7 +859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2390,22 +2375,22 @@
         <v>142</v>
       </c>
       <c r="C44" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="D44" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E44" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="D44" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E44" t="s" s="2">
-        <v>144</v>
-      </c>
       <c r="F44" t="s" s="2">
         <v>16</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>145</v>
+        <v>17</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>133</v>
+        <v>18</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>19</v>
@@ -2419,22 +2404,22 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="C45" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="B45" t="s" s="2">
+      <c r="D45" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E45" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="C45" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="D45" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E45" t="s" s="2">
+      <c r="F45" t="s" s="2">
         <v>148</v>
-      </c>
-      <c r="F45" t="s" s="2">
-        <v>16</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>17</v>
@@ -2460,16 +2445,16 @@
         <v>150</v>
       </c>
       <c r="C46" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="D46" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E46" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="D46" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E46" t="s" s="2">
-        <v>152</v>
-      </c>
       <c r="F46" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>17</v>
@@ -2489,22 +2474,22 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="D47" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E47" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="B47" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="D47" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E47" t="s" s="2">
-        <v>156</v>
-      </c>
       <c r="F47" t="s" s="2">
-        <v>153</v>
+        <v>16</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>17</v>
@@ -2524,19 +2509,19 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="D48" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E48" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="D48" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E48" t="s" s="2">
-        <v>159</v>
       </c>
       <c r="F48" t="s" s="2">
         <v>16</v>
@@ -2559,19 +2544,19 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="D49" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E49" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="D49" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E49" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="F49" t="s" s="2">
         <v>16</v>
@@ -2594,22 +2579,22 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="D50" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E50" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="B50" t="s" s="2">
+      <c r="F50" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="C50" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="D50" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E50" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="F50" t="s" s="2">
-        <v>16</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>17</v>
@@ -2629,22 +2614,22 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="B51" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="B51" t="s" s="2">
+      <c r="C51" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="D51" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E51" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="C51" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="D51" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E51" t="s" s="2">
-        <v>168</v>
-      </c>
       <c r="F51" t="s" s="2">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>17</v>
@@ -2664,22 +2649,22 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="D52" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E52" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="B52" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="D52" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E52" t="s" s="2">
-        <v>172</v>
-      </c>
       <c r="F52" t="s" s="2">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>17</v>
@@ -2699,22 +2684,22 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="C53" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="D53" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E53" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="B53" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="C53" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="D53" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E53" t="s" s="2">
-        <v>175</v>
-      </c>
       <c r="F53" t="s" s="2">
-        <v>169</v>
+        <v>16</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>17</v>
@@ -2734,22 +2719,22 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="C54" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="D54" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E54" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="B54" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="C54" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="D54" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E54" t="s" s="2">
-        <v>178</v>
-      </c>
       <c r="F54" t="s" s="2">
-        <v>16</v>
+        <v>148</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>17</v>
@@ -2769,22 +2754,22 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="C55" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="D55" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E55" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="B55" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="C55" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="D55" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E55" t="s" s="2">
-        <v>181</v>
-      </c>
       <c r="F55" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>17</v>
@@ -2804,22 +2789,22 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="C56" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="D56" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E56" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="B56" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C56" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="D56" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E56" t="s" s="2">
-        <v>184</v>
-      </c>
       <c r="F56" t="s" s="2">
-        <v>153</v>
+        <v>16</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>17</v>
@@ -2839,19 +2824,19 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="C57" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="B57" t="s" s="2">
+      <c r="D57" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E57" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="D57" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E57" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="F57" t="s" s="2">
         <v>16</v>
@@ -2874,22 +2859,22 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="B58" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="B58" t="s" s="2">
+      <c r="C58" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="D58" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E58" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="C58" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="D58" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E58" t="s" s="2">
-        <v>191</v>
-      </c>
       <c r="F58" t="s" s="2">
-        <v>16</v>
+        <v>164</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>17</v>
@@ -2909,22 +2894,22 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="D59" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E59" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="B59" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="C59" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="D59" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E59" t="s" s="2">
-        <v>194</v>
-      </c>
       <c r="F59" t="s" s="2">
-        <v>169</v>
+        <v>16</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>17</v>
@@ -2944,22 +2929,22 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="C60" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="D60" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E60" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="B60" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="C60" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="D60" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E60" t="s" s="2">
-        <v>197</v>
-      </c>
       <c r="F60" t="s" s="2">
-        <v>16</v>
+        <v>164</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>17</v>
@@ -2979,22 +2964,22 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="D61" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E61" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="B61" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="D61" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E61" t="s" s="2">
-        <v>200</v>
-      </c>
       <c r="F61" t="s" s="2">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>17</v>
@@ -3014,22 +2999,22 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="C62" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="D62" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E62" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="B62" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C62" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="D62" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E62" t="s" s="2">
-        <v>203</v>
-      </c>
       <c r="F62" t="s" s="2">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>17</v>
@@ -3049,22 +3034,22 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="C63" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="D63" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E63" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="B63" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="C63" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="D63" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E63" t="s" s="2">
-        <v>206</v>
-      </c>
       <c r="F63" t="s" s="2">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>17</v>
@@ -3084,22 +3069,22 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="C64" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="D64" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E64" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="B64" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="C64" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="D64" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E64" t="s" s="2">
-        <v>209</v>
-      </c>
       <c r="F64" t="s" s="2">
-        <v>169</v>
+        <v>16</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>17</v>
@@ -3119,19 +3104,19 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D65" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E65" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="D65" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E65" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="F65" t="s" s="2">
         <v>16</v>
@@ -3154,19 +3139,19 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="D66" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E66" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="C66" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D66" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E66" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="F66" t="s" s="2">
         <v>16</v>
@@ -3189,19 +3174,19 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="C67" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="D67" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E67" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="C67" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="D67" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E67" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="F67" t="s" s="2">
         <v>16</v>
@@ -3224,19 +3209,19 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="C68" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="D68" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E68" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="C68" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="D68" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E68" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="F68" t="s" s="2">
         <v>16</v>
@@ -3259,22 +3244,22 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="C69" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="D69" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E69" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="B69" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="C69" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="D69" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E69" t="s" s="2">
-        <v>224</v>
-      </c>
       <c r="F69" t="s" s="2">
-        <v>16</v>
+        <v>164</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>17</v>
@@ -3294,22 +3279,22 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="C70" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="D70" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E70" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="B70" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="C70" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="D70" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E70" t="s" s="2">
-        <v>227</v>
-      </c>
       <c r="F70" t="s" s="2">
-        <v>169</v>
+        <v>16</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>17</v>
@@ -3329,22 +3314,22 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="C71" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="D71" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E71" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="B71" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="C71" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="D71" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E71" t="s" s="2">
-        <v>230</v>
-      </c>
       <c r="F71" t="s" s="2">
-        <v>16</v>
+        <v>148</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>17</v>
@@ -3364,22 +3349,22 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="C72" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="D72" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E72" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="B72" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="C72" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="D72" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E72" t="s" s="2">
-        <v>233</v>
-      </c>
       <c r="F72" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>17</v>
@@ -3399,22 +3384,22 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="C73" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="D73" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E73" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="B73" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="C73" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="D73" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E73" t="s" s="2">
-        <v>236</v>
-      </c>
       <c r="F73" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>17</v>
@@ -3434,22 +3419,22 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="C74" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="D74" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E74" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="B74" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="C74" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="D74" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E74" t="s" s="2">
-        <v>239</v>
-      </c>
       <c r="F74" t="s" s="2">
-        <v>153</v>
+        <v>16</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>17</v>
@@ -3464,41 +3449,6 @@
         <v>14</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="C75" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="D75" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E75" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="F75" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K75" t="s" s="2">
         <v>14</v>
       </c>
     </row>

--- a/branches/main/observations-summary.xlsx
+++ b/branches/main/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="226">
   <si>
     <t>Profile</t>
   </si>
@@ -221,6 +221,24 @@
     <t>null#444479000, null#null, null#null</t>
   </si>
   <si>
+    <t>mii-pr-icu-ect-blutfluss-extrakorporaler-gasaustausch</t>
+  </si>
+  <si>
+    <t>MII PR ICU Blutfluss Extrakorporaler Gasaustausch</t>
+  </si>
+  <si>
+    <t>null#251288004, null#null, null#null</t>
+  </si>
+  <si>
+    <t>mii-pr-icu-ect-blutflussindex-extrakorporaler-gasaustausch</t>
+  </si>
+  <si>
+    <t>MII PR ICU Blutflussindex Extrakorporaler Gasaustausch</t>
+  </si>
+  <si>
+    <t>null#251289007, null#null, null#null</t>
+  </si>
+  <si>
     <t>mii-pr-icu-ect-dauer-extrakorporaler-gasaustausch</t>
   </si>
   <si>
@@ -257,6 +275,15 @@
     <t>null#401000124105, null#null, null#null</t>
   </si>
   <si>
+    <t>mii-pr-icu-ect-ionisiertes-kalzium-nierenersatzverfahren</t>
+  </si>
+  <si>
+    <t>MII PR ICU Ionisiertes Kalzium Nierenersatzverfahren</t>
+  </si>
+  <si>
+    <t>null#null, null#83064-6, null#null</t>
+  </si>
+  <si>
     <t>mii-pr-icu-ect-substituatfluss</t>
   </si>
   <si>
@@ -381,69 +408,6 @@
   </si>
   <si>
     <t>MII PR ICU Parameter von Extrakorporalen Verfahren</t>
-  </si>
-  <si>
-    <t>mii-pr-icu-score</t>
-  </si>
-  <si>
-    <t>MII PR ICU Score</t>
-  </si>
-  <si>
-    <t>Observation Category Codes#survey, SNOMED CT#273249006</t>
-  </si>
-  <si>
-    <t>Quantityĵ, CodeableConceptĵ, integerĵ</t>
-  </si>
-  <si>
-    <t>mii-pr-icu-score-faces-pain-scale-revised</t>
-  </si>
-  <si>
-    <t>MII PR ICU Score Faces Pain Scale Revised</t>
-  </si>
-  <si>
-    <t>null#1284909003</t>
-  </si>
-  <si>
-    <t>mii-pr-icu-score-gcs</t>
-  </si>
-  <si>
-    <t>MII PR ICU Score GCS</t>
-  </si>
-  <si>
-    <t>null#9269-2, null#248241002, null#153728</t>
-  </si>
-  <si>
-    <t>CodeableConceptĵ</t>
-  </si>
-  <si>
-    <t>LOINC#9267-6</t>
-  </si>
-  <si>
-    <t>LOINC#9268-4</t>
-  </si>
-  <si>
-    <t>LOINC#9270-0</t>
-  </si>
-  <si>
-    <t>mii-pr-icu-score-numerische-ratingskala</t>
-  </si>
-  <si>
-    <t>MII PR ICU Score Numerische Ratingskala</t>
-  </si>
-  <si>
-    <t>null#1284857008</t>
-  </si>
-  <si>
-    <t>integerĵ</t>
-  </si>
-  <si>
-    <t>mii-pr-icu-score-visuelle-analogskala</t>
-  </si>
-  <si>
-    <t>MII PR ICU Score Visuelle Analogskala</t>
-  </si>
-  <si>
-    <t>null#38214-3, null#443394008</t>
   </si>
   <si>
     <t>mii-pr-icu-vent-atemwegsdruck-mittlerem-expiratorischem-gasfluss</t>
@@ -859,7 +823,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K74"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1745,25 +1709,25 @@
         <v>91</v>
       </c>
       <c r="C26" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="D26" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E26" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="D26" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E26" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="F26" t="s" s="2">
-        <v>94</v>
+        <v>16</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>17</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="J26" t="s" s="2">
         <v>14</v>
@@ -1774,25 +1738,25 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F27" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>18</v>
@@ -1809,25 +1773,25 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F28" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>18</v>
@@ -1844,31 +1808,31 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F29" t="s" s="2">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="J29" t="s" s="2">
         <v>14</v>
@@ -1879,25 +1843,25 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>99</v>
+        <v>14</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>100</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>92</v>
+        <v>14</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F30" t="s" s="2">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>18</v>
@@ -1914,25 +1878,25 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>92</v>
+        <v>14</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F31" t="s" s="2">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>18</v>
@@ -1949,28 +1913,28 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>105</v>
+        <v>14</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C32" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D32" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E32" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="D32" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E32" t="s" s="2">
-        <v>108</v>
-      </c>
       <c r="F32" t="s" s="2">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>109</v>
+        <v>18</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>19</v>
@@ -1984,28 +1948,28 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="D33" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E33" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="B33" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="D33" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E33" t="s" s="2">
-        <v>112</v>
-      </c>
       <c r="F33" t="s" s="2">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>17</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>109</v>
+        <v>18</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>19</v>
@@ -2019,22 +1983,22 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="D34" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E34" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="B34" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="D34" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E34" t="s" s="2">
-        <v>115</v>
-      </c>
       <c r="F34" t="s" s="2">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>17</v>
@@ -2054,34 +2018,34 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="C35" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="B35" t="s" s="2">
+      <c r="D35" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E35" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="C35" t="s" s="2">
+      <c r="F35" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H35" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="D35" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E35" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="F35" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="G35" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H35" t="s" s="2">
-        <v>109</v>
-      </c>
       <c r="I35" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>120</v>
+        <v>14</v>
       </c>
       <c r="K35" t="s" s="2">
         <v>14</v>
@@ -2089,28 +2053,28 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="D36" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E36" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="B36" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="D36" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E36" t="s" s="2">
-        <v>15</v>
-      </c>
       <c r="F36" t="s" s="2">
-        <v>16</v>
+        <v>103</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>17</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>18</v>
+        <v>118</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>19</v>
@@ -2124,28 +2088,28 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="B37" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="B37" t="s" s="2">
+      <c r="C37" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="D37" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E37" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="C37" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="D37" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E37" t="s" s="2">
-        <v>14</v>
-      </c>
       <c r="F37" t="s" s="2">
-        <v>16</v>
+        <v>103</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>17</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>126</v>
+        <v>18</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>19</v>
@@ -2159,34 +2123,34 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="C38" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="B38" t="s" s="2">
+      <c r="D38" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E38" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="C38" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="D38" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E38" t="s" s="2">
+      <c r="F38" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J38" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="F38" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G38" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H38" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I38" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>14</v>
       </c>
       <c r="K38" t="s" s="2">
         <v>14</v>
@@ -2200,13 +2164,13 @@
         <v>131</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>125</v>
+        <v>64</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>132</v>
+        <v>15</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>16</v>
@@ -2229,28 +2193,28 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>14</v>
+        <v>132</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>14</v>
+        <v>135</v>
       </c>
       <c r="F40" t="s" s="2">
-        <v>14</v>
+        <v>136</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>133</v>
+        <v>18</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>19</v>
@@ -2259,33 +2223,33 @@
         <v>14</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>134</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>14</v>
+        <v>137</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E41" t="s" s="2">
-        <v>14</v>
+        <v>139</v>
       </c>
       <c r="F41" t="s" s="2">
-        <v>14</v>
+        <v>136</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>133</v>
+        <v>18</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>19</v>
@@ -2294,33 +2258,33 @@
         <v>14</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>135</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>14</v>
+        <v>140</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E42" t="s" s="2">
-        <v>14</v>
+        <v>142</v>
       </c>
       <c r="F42" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>133</v>
+        <v>18</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>19</v>
@@ -2329,24 +2293,24 @@
         <v>14</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>136</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>16</v>
@@ -2355,7 +2319,7 @@
         <v>17</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>19</v>
@@ -2369,19 +2333,19 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>16</v>
@@ -2404,22 +2368,22 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F45" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>17</v>
@@ -2439,22 +2403,22 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F46" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>17</v>
@@ -2474,22 +2438,22 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="D47" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E47" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="F47" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="D47" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E47" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="F47" t="s" s="2">
-        <v>16</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>17</v>
@@ -2509,19 +2473,19 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E48" t="s" s="2">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="F48" t="s" s="2">
         <v>16</v>
@@ -2544,22 +2508,22 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F49" t="s" s="2">
-        <v>16</v>
+        <v>136</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>17</v>
@@ -2579,22 +2543,22 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F50" t="s" s="2">
-        <v>164</v>
+        <v>136</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>17</v>
@@ -2614,22 +2578,22 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F51" t="s" s="2">
-        <v>164</v>
+        <v>16</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>17</v>
@@ -2649,22 +2613,22 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="F52" t="s" s="2">
-        <v>164</v>
+        <v>16</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>17</v>
@@ -2684,22 +2648,22 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F53" t="s" s="2">
-        <v>16</v>
+        <v>152</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>17</v>
@@ -2719,22 +2683,22 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F54" t="s" s="2">
-        <v>148</v>
+        <v>16</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>17</v>
@@ -2754,22 +2718,22 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E55" t="s" s="2">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="F55" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>17</v>
@@ -2789,22 +2753,22 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E56" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="F56" t="s" s="2">
-        <v>16</v>
+        <v>136</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>17</v>
@@ -2824,22 +2788,22 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>185</v>
+        <v>134</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E57" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F57" t="s" s="2">
-        <v>16</v>
+        <v>152</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>17</v>
@@ -2859,22 +2823,22 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E58" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F58" t="s" s="2">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>17</v>
@@ -2894,19 +2858,19 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>185</v>
+        <v>134</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E59" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F59" t="s" s="2">
         <v>16</v>
@@ -2929,22 +2893,22 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>185</v>
+        <v>14</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E60" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F60" t="s" s="2">
-        <v>164</v>
+        <v>16</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>17</v>
@@ -2964,22 +2928,22 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>185</v>
+        <v>134</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E61" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F61" t="s" s="2">
-        <v>148</v>
+        <v>16</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>17</v>
@@ -2999,22 +2963,22 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E62" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F62" t="s" s="2">
-        <v>164</v>
+        <v>16</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>17</v>
@@ -3034,22 +2998,22 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F63" t="s" s="2">
-        <v>164</v>
+        <v>16</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>17</v>
@@ -3069,22 +3033,22 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F64" t="s" s="2">
-        <v>16</v>
+        <v>152</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>17</v>
@@ -3104,19 +3068,19 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F65" t="s" s="2">
         <v>16</v>
@@ -3139,22 +3103,22 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E66" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F66" t="s" s="2">
-        <v>16</v>
+        <v>136</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>17</v>
@@ -3174,22 +3138,22 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="D67" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E67" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F67" t="s" s="2">
-        <v>16</v>
+        <v>136</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>17</v>
@@ -3209,22 +3173,22 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E68" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F68" t="s" s="2">
-        <v>16</v>
+        <v>136</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>17</v>
@@ -3244,22 +3208,22 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E69" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F69" t="s" s="2">
-        <v>164</v>
+        <v>16</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>17</v>
@@ -3274,181 +3238,6 @@
         <v>14</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="C70" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="D70" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E70" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="F70" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G70" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H70" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K70" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="C71" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="D71" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E71" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="F71" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="C72" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="D72" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E72" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="F72" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="C73" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="D73" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E73" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="F73" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="C74" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="D74" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E74" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="F74" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K74" t="s" s="2">
         <v>14</v>
       </c>
     </row>
